--- a/cluster_topology_import_template_v2.xlsx
+++ b/cluster_topology_import_template_v2.xlsx
@@ -681,7 +681,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>必填，如: db-server-01</t>
+          <t>可选，留空则根据IP自动生成，如: node-192.168.1.10</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -728,7 +728,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>生产环境</t>
+          <t>示例数据-生产环境</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>生产环境</t>
+          <t>示例数据-生产环境</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -862,7 +862,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>测试环境</t>
+          <t>示例数据-测试环境</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -1127,7 +1127,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>192.168.1.10</t>
+          <t>示例数据-192.168.1.10</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>192.168.1.11</t>
+          <t>示例数据-192.168.1.11</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -1231,7 +1231,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>192.168.2.10</t>
+          <t>示例数据-192.168.2.10</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
